--- a/public/upload/export_excel/บิลค่าเช่า-03-2026.xlsx
+++ b/public/upload/export_excel/บิลค่าเช่า-03-2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
   <si>
     <t>สาขาเจริญใจ</t>
   </si>
@@ -33,6 +33,66 @@
   </si>
   <si>
     <t>สถานะบิล</t>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>บริษัท Katao Uu</t>
+  </si>
+  <si>
+    <t>62,025</t>
+  </si>
+  <si>
+    <t>ไม่สมบูรณ์</t>
+  </si>
+  <si>
+    <t>A104</t>
+  </si>
+  <si>
+    <t>นางสาว วันศุกร์ เทสระบบ</t>
+  </si>
+  <si>
+    <t>6,300</t>
+  </si>
+  <si>
+    <t>A305</t>
+  </si>
+  <si>
+    <t>บริษัท Central park</t>
+  </si>
+  <si>
+    <t>4,300</t>
+  </si>
+  <si>
+    <t>A306</t>
+  </si>
+  <si>
+    <t>บริษัท Central park hotel jjj</t>
+  </si>
+  <si>
+    <t>5,200</t>
+  </si>
+  <si>
+    <t>A311</t>
+  </si>
+  <si>
+    <t>บริษัท Orange เทส1</t>
+  </si>
+  <si>
+    <t>3,000</t>
+  </si>
+  <si>
+    <t>A312</t>
+  </si>
+  <si>
+    <t>A313</t>
+  </si>
+  <si>
+    <t>A314</t>
+  </si>
+  <si>
+    <t>บริษัท เวกทดสอบ ทำสัญญา</t>
   </si>
 </sst>
 </file>
@@ -375,7 +435,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -406,6 +466,118 @@
       </c>
       <c r="D3" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
